--- a/AAII_Financials/Quarterly/PODC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PODC_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="92">
   <si>
     <t>PODC</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,148 +656,173 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E8" s="3">
+        <v>10500</v>
+      </c>
+      <c r="F8" s="3">
         <v>10600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>8600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>8500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>8700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>8200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>8100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>16000</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>9100</v>
+      </c>
+      <c r="F9" s="3">
         <v>8200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>7000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>6300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>6600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>6700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>6000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>13500</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F10" s="3">
         <v>2400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>2200</v>
-      </c>
-      <c r="G10" s="3">
-        <v>2100</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1500</v>
       </c>
       <c r="I10" s="3">
         <v>2100</v>
       </c>
       <c r="J10" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K10" s="3">
+        <v>2100</v>
+      </c>
+      <c r="L10" s="3">
         <v>2500</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -809,8 +834,10 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -838,8 +865,14 @@
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -867,51 +900,63 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>2200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>-2200</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>-600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-500</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>300</v>
+      </c>
+      <c r="E15" s="3">
+        <v>200</v>
+      </c>
+      <c r="F15" s="3">
         <v>100</v>
       </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
       <c r="G15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
         <v>100</v>
@@ -920,13 +965,19 @@
         <v>100</v>
       </c>
       <c r="J15" s="3">
+        <v>100</v>
+      </c>
+      <c r="K15" s="3">
+        <v>100</v>
+      </c>
+      <c r="L15" s="3">
         <v>300</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -935,66 +986,80 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>11900</v>
+      </c>
+      <c r="F17" s="3">
         <v>10400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>11500</v>
       </c>
-      <c r="F17" s="3">
-        <v>6100</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>8300</v>
+      </c>
+      <c r="I17" s="3">
         <v>9200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>8900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>8500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>18600</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F18" s="3">
         <v>200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-2900</v>
       </c>
-      <c r="F18" s="3">
-        <v>2400</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>200</v>
+      </c>
+      <c r="I18" s="3">
         <v>-500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-2600</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1006,124 +1071,150 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="F20" s="3">
         <v>1200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>700</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="F21" s="3">
         <v>1500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-2500</v>
       </c>
-      <c r="F21" s="3">
-        <v>3200</v>
-      </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I21" s="3">
         <v>-400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-600</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3">
         <v>-2200</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>700</v>
+      </c>
+      <c r="F22" s="3">
         <v>1600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>1700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>1400</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
       <c r="I22" s="3">
         <v>0</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="F23" s="3">
         <v>-200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-4200</v>
       </c>
-      <c r="F23" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J23" s="3">
         <v>-700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-2500</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1151,8 +1242,14 @@
       <c r="K24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1180,66 +1277,84 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="F26" s="3">
         <v>-200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-4200</v>
       </c>
-      <c r="F26" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J26" s="3">
         <v>-700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-2500</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="F27" s="3">
         <v>-200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-4200</v>
       </c>
-      <c r="F27" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J27" s="3">
         <v>-700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-2500</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1267,8 +1382,14 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1296,8 +1417,14 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1325,8 +1452,14 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1354,66 +1487,84 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>8800</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-700</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="F33" s="3">
         <v>-200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-4200</v>
       </c>
-      <c r="F33" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J33" s="3">
         <v>-700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-2500</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1441,71 +1592,89 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="F35" s="3">
         <v>-200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-4200</v>
       </c>
-      <c r="F35" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J35" s="3">
         <v>-700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-2500</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1517,8 +1686,10 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1530,26 +1701,28 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E41" s="3">
         <v>500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
+        <v>500</v>
+      </c>
+      <c r="G41" s="3">
         <v>4000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>4100</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1559,8 +1732,14 @@
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1588,26 +1767,32 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>9700</v>
+      </c>
+      <c r="F43" s="3">
         <v>8800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>6300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>7100</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1617,8 +1802,14 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1646,26 +1837,32 @@
       <c r="K44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F45" s="3">
         <v>1100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>700</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1675,26 +1872,32 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>11200</v>
+      </c>
+      <c r="F46" s="3">
         <v>10400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>10800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>12000</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1704,26 +1907,32 @@
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E47" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F47" s="3">
         <v>3800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>4600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>5500</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1733,13 +1942,19 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E48" s="3">
         <v>200</v>
@@ -1747,11 +1962,11 @@
       <c r="F48" s="3">
         <v>200</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
+      <c r="G48" s="3">
+        <v>200</v>
+      </c>
+      <c r="H48" s="3">
+        <v>200</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
@@ -1762,26 +1977,32 @@
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>14900</v>
+      </c>
+      <c r="F49" s="3">
         <v>12700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>12800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>12800</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I49" s="3" t="s">
         <v>3</v>
       </c>
@@ -1791,8 +2012,14 @@
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1820,8 +2047,14 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1849,8 +2082,14 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -1878,8 +2117,14 @@
       <c r="K52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1907,26 +2152,32 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>27700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>28400</v>
+      </c>
+      <c r="F54" s="3">
         <v>27200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>28500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>30600</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
       </c>
@@ -1936,8 +2187,14 @@
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1949,8 +2206,10 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1962,26 +2221,28 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F57" s="3">
         <v>2000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2100</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
       </c>
@@ -1991,26 +2252,32 @@
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>5600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>5700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>4300</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2020,26 +2287,32 @@
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>9500</v>
+      </c>
+      <c r="F59" s="3">
         <v>12600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>10900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>11800</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2049,26 +2322,32 @@
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>10900</v>
+      </c>
+      <c r="F60" s="3">
         <v>20200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>17700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>18100</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2078,8 +2357,14 @@
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2107,37 +2392,49 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2165,8 +2462,14 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2194,8 +2497,14 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2223,26 +2532,32 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>11100</v>
+      </c>
+      <c r="F66" s="3">
         <v>20200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>17700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>18100</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2252,8 +2567,14 @@
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2265,8 +2586,10 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2294,8 +2617,14 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2323,8 +2652,14 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2352,8 +2687,14 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2381,26 +2722,32 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-28600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-12900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-8700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-6300</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2410,8 +2757,14 @@
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2439,8 +2792,14 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2468,8 +2827,14 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2497,26 +2862,32 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>17300</v>
+      </c>
+      <c r="F76" s="3">
         <v>7000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>10800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>12400</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2526,8 +2897,14 @@
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2555,71 +2932,89 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="F81" s="3">
         <v>-200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-4200</v>
       </c>
-      <c r="F81" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J81" s="3">
         <v>-700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-2500</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2631,16 +3026,18 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F83" s="3">
         <v>100</v>
@@ -2651,17 +3048,23 @@
       <c r="H83" s="3">
         <v>100</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+      <c r="I83" s="3">
+        <v>100</v>
+      </c>
+      <c r="J83" s="3">
+        <v>100</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2689,8 +3092,14 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2718,8 +3127,14 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2747,8 +3162,14 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2776,8 +3197,14 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2805,37 +3232,49 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E89" s="3">
+        <v>600</v>
+      </c>
+      <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
         <v>-500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-4700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1000</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2847,16 +3286,18 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="E91" s="3">
-        <v>-100</v>
+        <v>-600</v>
       </c>
       <c r="F91" s="3">
         <v>-100</v>
@@ -2868,16 +3309,22 @@
         <v>-100</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2905,8 +3352,14 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2934,19 +3387,25 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E94" s="3">
-        <v>-100</v>
+        <v>-600</v>
       </c>
       <c r="F94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G94" s="3">
         <v>-100</v>
@@ -2954,17 +3413,23 @@
       <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+      <c r="I94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-100</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2976,8 +3441,10 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3005,8 +3472,14 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3034,8 +3507,14 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3063,8 +3542,14 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3092,37 +3577,49 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-3000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>7000</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3150,33 +3647,45 @@
       <c r="K101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-3100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>2200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-1100</v>
       </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PODC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PODC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
   <si>
     <t>PODC</t>
   </si>
@@ -656,173 +656,199 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3">
         <v>10400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>10500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>10600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>8600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>8500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>8700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>8200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>8100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>16000</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E9" s="3">
+        <v>10700</v>
+      </c>
+      <c r="F9" s="3">
         <v>9400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>9100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>8200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>7000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>6300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>6600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>6700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>6000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>13500</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="3">
         <v>1000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>2400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>1600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>2200</v>
-      </c>
-      <c r="I10" s="3">
-        <v>2100</v>
-      </c>
-      <c r="J10" s="3">
-        <v>1500</v>
       </c>
       <c r="K10" s="3">
         <v>2100</v>
       </c>
       <c r="L10" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M10" s="3">
+        <v>2100</v>
+      </c>
+      <c r="N10" s="3">
         <v>2500</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -836,8 +862,10 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -871,8 +899,14 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -906,13 +940,19 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>200</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -920,49 +960,55 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>2200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>-2200</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>-600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-500</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>400</v>
+      </c>
+      <c r="E15" s="3">
+        <v>400</v>
+      </c>
+      <c r="F15" s="3">
         <v>300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>200</v>
-      </c>
-      <c r="F15" s="3">
-        <v>100</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
       </c>
       <c r="H15" s="3">
         <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
         <v>100</v>
@@ -971,13 +1017,19 @@
         <v>100</v>
       </c>
       <c r="L15" s="3">
+        <v>100</v>
+      </c>
+      <c r="M15" s="3">
+        <v>100</v>
+      </c>
+      <c r="N15" s="3">
         <v>300</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -988,78 +1040,92 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>12900</v>
+      </c>
+      <c r="F17" s="3">
         <v>13000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>11900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>10400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>11500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>8300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>9200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>8900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>8500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>18600</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1400</v>
-      </c>
-      <c r="F18" s="3">
-        <v>200</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-2900</v>
       </c>
       <c r="H18" s="3">
         <v>200</v>
       </c>
       <c r="I18" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="J18" s="3">
+        <v>200</v>
+      </c>
+      <c r="K18" s="3">
         <v>-500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-2600</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1073,78 +1139,92 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
         <v>0</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-8800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>1200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>700</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="3">
         <v>-2200</v>
       </c>
-      <c r="E21" s="3">
-        <v>-10000</v>
-      </c>
-      <c r="F21" s="3">
-        <v>1500</v>
-      </c>
       <c r="G21" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I21" s="3">
         <v>-2500</v>
       </c>
-      <c r="H21" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K21" s="3">
         <v>-400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-600</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>-2200</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1152,69 +1232,81 @@
         <v>0</v>
       </c>
       <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
         <v>700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>1600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>1700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>1400</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F23" s="3">
         <v>-2600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-10900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-4200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-2500</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1222,13 +1314,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H24" s="3">
         <v>0</v>
@@ -1248,8 +1340,14 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1283,78 +1381,96 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="3">
         <v>-2600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-10900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-4200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-2500</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="3">
         <v>-2600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-10900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-4200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-2500</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1388,8 +1504,14 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1423,8 +1545,14 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1458,8 +1586,14 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1493,78 +1627,96 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
         <v>0</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>8800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-1200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-700</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F33" s="3">
         <v>-2600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-10900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-4200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-2500</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1598,83 +1750,101 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F35" s="3">
         <v>-2600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-10900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-4200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-2500</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1688,8 +1858,10 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1703,32 +1875,34 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>900</v>
+      </c>
+      <c r="E41" s="3">
         <v>1400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G41" s="3">
         <v>500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>4000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>4100</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1738,8 +1912,14 @@
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1773,32 +1953,38 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F43" s="3">
         <v>7800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>9700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>8800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>6300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>7100</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1808,8 +1994,14 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1843,32 +2035,38 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F45" s="3">
         <v>400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>700</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1878,32 +2076,38 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>8600</v>
+      </c>
+      <c r="F46" s="3">
         <v>9600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>11200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>10400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>10800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>12000</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1913,32 +2117,38 @@
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3">
+        <v>100</v>
+      </c>
+      <c r="F47" s="3">
         <v>2700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>2200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>3800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>4600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>5500</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1948,8 +2158,14 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -1957,10 +2173,10 @@
         <v>300</v>
       </c>
       <c r="E48" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F48" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G48" s="3">
         <v>200</v>
@@ -1968,11 +2184,11 @@
       <c r="H48" s="3">
         <v>200</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+      <c r="I48" s="3">
+        <v>200</v>
+      </c>
+      <c r="J48" s="3">
+        <v>200</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -1983,32 +2199,38 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E49" s="3">
+        <v>15200</v>
+      </c>
+      <c r="F49" s="3">
         <v>15100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>14900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>12700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>12800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>12800</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2018,8 +2240,14 @@
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2053,8 +2281,14 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2088,8 +2322,14 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2123,8 +2363,14 @@
       <c r="M52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2158,32 +2404,38 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>24100</v>
+      </c>
+      <c r="F54" s="3">
         <v>27700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>28400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>27200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>28500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>30600</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2193,8 +2445,14 @@
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2208,8 +2466,10 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2223,32 +2483,34 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>7400</v>
+      </c>
+      <c r="F57" s="3">
         <v>1500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2100</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2258,32 +2520,38 @@
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>0</v>
+      <c r="D58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
       </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>5600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>5700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>4300</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2293,32 +2561,38 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>300</v>
+      </c>
+      <c r="F59" s="3">
         <v>9400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>9500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>12600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>10900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>11800</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2328,32 +2602,38 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>7700</v>
+      </c>
+      <c r="F60" s="3">
         <v>10900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>10900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>20200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>17700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>18100</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2363,8 +2643,14 @@
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2398,23 +2684,29 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3">
+        <v>100</v>
+      </c>
+      <c r="F62" s="3">
         <v>300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>300</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2424,17 +2716,23 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2468,8 +2766,14 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2503,8 +2807,14 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2538,32 +2848,38 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>7800</v>
+      </c>
+      <c r="F66" s="3">
         <v>11200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>11100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>20200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>17700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>18100</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2573,8 +2889,14 @@
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2588,8 +2910,10 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2623,8 +2947,14 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2658,8 +2988,14 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2693,8 +3029,14 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2728,32 +3070,38 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-29600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-28600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-26000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-12900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-8700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-6300</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2763,8 +3111,14 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2798,8 +3152,14 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2833,8 +3193,14 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2868,32 +3234,38 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>16300</v>
+      </c>
+      <c r="F76" s="3">
         <v>16500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>17300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>7000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>10800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>12400</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2903,8 +3275,14 @@
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2938,83 +3316,101 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F81" s="3">
         <v>-2600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-10900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-4200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-2500</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3028,43 +3424,51 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
         <v>400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3">
+        <v>400</v>
+      </c>
+      <c r="G83" s="3">
         <v>300</v>
       </c>
-      <c r="F83" s="3">
-        <v>100</v>
-      </c>
-      <c r="G83" s="3">
-        <v>100</v>
-      </c>
       <c r="H83" s="3">
-        <v>100</v>
+        <v>-200</v>
       </c>
       <c r="I83" s="3">
         <v>100</v>
       </c>
       <c r="J83" s="3">
+        <v>200</v>
+      </c>
+      <c r="K83" s="3">
         <v>100</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
+      <c r="L83" s="3">
+        <v>100</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3098,8 +3502,14 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3133,8 +3543,14 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3168,8 +3584,14 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3203,8 +3625,14 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3238,43 +3666,55 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F89" s="3">
         <v>1200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>600</v>
       </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
+        <v>4300</v>
+      </c>
+      <c r="I89" s="3">
         <v>-500</v>
       </c>
-      <c r="H89" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="K89" s="3">
         <v>900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1000</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3288,19 +3728,21 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-600</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-100</v>
       </c>
       <c r="G91" s="3">
         <v>-100</v>
@@ -3315,16 +3757,22 @@
         <v>-100</v>
       </c>
       <c r="K91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3358,8 +3806,14 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3393,25 +3847,31 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3">
         <v>-300</v>
       </c>
-      <c r="E94" s="3">
-        <v>-600</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
-        <v>-100</v>
+        <v>-700</v>
       </c>
       <c r="H94" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="I94" s="3">
         <v>-100</v>
@@ -3419,17 +3879,23 @@
       <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
+      <c r="K94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L94" s="3">
+        <v>-100</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3443,8 +3909,10 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3478,8 +3946,14 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3513,8 +3987,14 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3548,8 +4028,14 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3583,43 +4069,55 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
         <v>0</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-3000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="I100" s="3">
         <v>400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>7000</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3653,39 +4151,51 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F102" s="3">
         <v>900</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="I102" s="3">
         <v>-200</v>
       </c>
-      <c r="H102" s="3">
-        <v>2200</v>
-      </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K102" s="3">
         <v>800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1100</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PODC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PODC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="92">
   <si>
     <t>PODC</t>
   </si>
@@ -656,199 +656,213 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
-        <v>44926</v>
-      </c>
       <c r="J7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E8" s="3">
         <v>13200</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F8" s="3">
+        <v>11700</v>
+      </c>
+      <c r="G8" s="3">
         <v>10400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>10500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>10600</v>
       </c>
-      <c r="I8" s="3">
-        <v>8600</v>
-      </c>
       <c r="J8" s="3">
+        <v>8800</v>
+      </c>
+      <c r="K8" s="3">
         <v>8500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>16000</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E9" s="3">
         <v>11700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>9100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8200</v>
       </c>
-      <c r="I9" s="3">
-        <v>7000</v>
-      </c>
       <c r="J9" s="3">
+        <v>7600</v>
+      </c>
+      <c r="K9" s="3">
         <v>6300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13500</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1500</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="F10" s="3">
         <v>1000</v>
       </c>
       <c r="G10" s="3">
-        <v>1400</v>
+        <v>1100</v>
       </c>
       <c r="H10" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I10" s="3">
         <v>2400</v>
       </c>
-      <c r="I10" s="3">
-        <v>1600</v>
-      </c>
       <c r="J10" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K10" s="3">
         <v>2200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2500</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -864,31 +878,32 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
+        <v>200</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
@@ -905,8 +920,11 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,17 +964,20 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>200</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
@@ -966,52 +987,55 @@
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
-        <v>2200</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>-2200</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>-600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-500</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E15" s="3">
         <v>400</v>
       </c>
       <c r="F15" s="3">
+        <v>400</v>
+      </c>
+      <c r="G15" s="3">
         <v>300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>200</v>
       </c>
-      <c r="H15" s="3">
-        <v>100</v>
-      </c>
       <c r="I15" s="3">
         <v>0</v>
       </c>
       <c r="J15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>100</v>
@@ -1023,13 +1047,16 @@
         <v>100</v>
       </c>
       <c r="N15" s="3">
+        <v>100</v>
+      </c>
+      <c r="O15" s="3">
         <v>300</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1042,90 +1069,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>14500</v>
+        <v>13800</v>
       </c>
       <c r="E17" s="3">
+        <v>14300</v>
+      </c>
+      <c r="F17" s="3">
         <v>12900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>11900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>10400</v>
       </c>
-      <c r="I17" s="3">
-        <v>11500</v>
-      </c>
       <c r="J17" s="3">
+        <v>9700</v>
+      </c>
+      <c r="K17" s="3">
         <v>8300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>18600</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>3</v>
+        <v>-1700</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1200</v>
       </c>
       <c r="F18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="G18" s="3">
         <v>-2600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>200</v>
       </c>
-      <c r="I18" s="3">
-        <v>-2900</v>
-      </c>
       <c r="J18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="K18" s="3">
         <v>200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2600</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1141,35 +1175,36 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-8800</v>
+        <v>-200</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H20" s="3">
-        <v>1200</v>
+        <v>8800</v>
       </c>
       <c r="I20" s="3">
-        <v>300</v>
+        <v>-1200</v>
       </c>
       <c r="J20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K20" s="3">
         <v>700</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1177,81 +1212,87 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-900</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
+        <v>-1300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-800</v>
       </c>
       <c r="F21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="K21" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
         <v>-2200</v>
       </c>
-      <c r="G21" s="3">
-        <v>-9900</v>
-      </c>
-      <c r="H21" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="J21" s="3">
-        <v>1100</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-400</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-600</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3">
         <v>700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1600</v>
       </c>
-      <c r="I22" s="3">
-        <v>1700</v>
-      </c>
       <c r="J22" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K22" s="3">
         <v>1400</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -1261,75 +1302,81 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-200</v>
       </c>
-      <c r="I23" s="3">
-        <v>-4200</v>
-      </c>
       <c r="J23" s="3">
-        <v>-500</v>
+        <v>-4000</v>
       </c>
       <c r="K23" s="3">
         <v>-500</v>
       </c>
       <c r="L23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M23" s="3">
         <v>-700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2500</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
         <v>0</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1346,8 +1393,11 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1387,90 +1437,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1400</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G26" s="3">
         <v>-2600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-10900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-200</v>
       </c>
-      <c r="I26" s="3">
-        <v>-4200</v>
-      </c>
       <c r="J26" s="3">
-        <v>-500</v>
+        <v>-4000</v>
       </c>
       <c r="K26" s="3">
         <v>-500</v>
       </c>
       <c r="L26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M26" s="3">
         <v>-700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2500</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1400</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G27" s="3">
         <v>-2600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-10900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-200</v>
       </c>
-      <c r="I27" s="3">
-        <v>-4200</v>
-      </c>
       <c r="J27" s="3">
-        <v>-500</v>
+        <v>-4000</v>
       </c>
       <c r="K27" s="3">
         <v>-500</v>
       </c>
       <c r="L27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M27" s="3">
         <v>-700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2500</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1510,8 +1569,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1551,8 +1613,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1592,8 +1657,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1633,35 +1701,38 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>8800</v>
+        <v>200</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H32" s="3">
-        <v>-1200</v>
+        <v>-8800</v>
       </c>
       <c r="I32" s="3">
-        <v>-300</v>
+        <v>1200</v>
       </c>
       <c r="J32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="K32" s="3">
         <v>-700</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -1669,54 +1740,60 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1400</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G33" s="3">
         <v>-2600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-10900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-200</v>
       </c>
-      <c r="I33" s="3">
-        <v>-4200</v>
-      </c>
       <c r="J33" s="3">
-        <v>-500</v>
+        <v>-4000</v>
       </c>
       <c r="K33" s="3">
         <v>-500</v>
       </c>
       <c r="L33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M33" s="3">
         <v>-700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2500</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1756,95 +1833,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1400</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G35" s="3">
         <v>-2600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-10900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-200</v>
       </c>
-      <c r="I35" s="3">
-        <v>-4200</v>
-      </c>
       <c r="J35" s="3">
-        <v>-500</v>
+        <v>-4000</v>
       </c>
       <c r="K35" s="3">
         <v>-500</v>
       </c>
       <c r="L35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M35" s="3">
         <v>-700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2500</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
-        <v>44926</v>
-      </c>
       <c r="J38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1860,8 +1946,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1877,35 +1964,36 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E41" s="3">
         <v>900</v>
-      </c>
-      <c r="E41" s="3">
-        <v>1400</v>
       </c>
       <c r="F41" s="3">
         <v>1400</v>
       </c>
       <c r="G41" s="3">
-        <v>500</v>
+        <v>1400</v>
       </c>
       <c r="H41" s="3">
         <v>500</v>
       </c>
       <c r="I41" s="3">
-        <v>4000</v>
+        <v>500</v>
       </c>
       <c r="J41" s="3">
+        <v>3600</v>
+      </c>
+      <c r="K41" s="3">
         <v>4100</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1918,8 +2006,11 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1959,35 +2050,38 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E43" s="3">
         <v>7100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8800</v>
       </c>
-      <c r="I43" s="3">
-        <v>6300</v>
-      </c>
       <c r="J43" s="3">
+        <v>6900</v>
+      </c>
+      <c r="K43" s="3">
         <v>7100</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2000,31 +2094,34 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2041,35 +2138,38 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>1200</v>
-      </c>
-      <c r="E45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="F45" s="3">
-        <v>400</v>
-      </c>
-      <c r="G45" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I45" s="3">
-        <v>600</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>700</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2082,35 +2182,38 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E46" s="3">
         <v>9200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10400</v>
       </c>
-      <c r="I46" s="3">
-        <v>10800</v>
-      </c>
       <c r="J46" s="3">
+        <v>11400</v>
+      </c>
+      <c r="K46" s="3">
         <v>12000</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2123,35 +2226,38 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>100</v>
-      </c>
-      <c r="F47" s="3">
-        <v>2700</v>
-      </c>
-      <c r="G47" s="3">
-        <v>2200</v>
-      </c>
-      <c r="H47" s="3">
-        <v>3800</v>
-      </c>
-      <c r="I47" s="3">
-        <v>4600</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3">
         <v>5500</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2164,8 +2270,11 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2179,7 +2288,7 @@
         <v>300</v>
       </c>
       <c r="G48" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="H48" s="3">
         <v>200</v>
@@ -2190,8 +2299,8 @@
       <c r="J48" s="3">
         <v>200</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
+      <c r="K48" s="3">
+        <v>200</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
@@ -2205,34 +2314,37 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E49" s="3">
         <v>14500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>15200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>15100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>12700</v>
-      </c>
-      <c r="I49" s="3">
-        <v>12800</v>
       </c>
       <c r="J49" s="3">
         <v>12800</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
+      <c r="K49" s="3">
+        <v>12800</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
@@ -2246,8 +2358,11 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2287,8 +2402,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,31 +2446,34 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -2369,8 +2490,11 @@
       <c r="O52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2410,35 +2534,38 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E54" s="3">
         <v>24000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>24100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>27700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>28400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>27200</v>
       </c>
-      <c r="I54" s="3">
-        <v>28500</v>
-      </c>
       <c r="J54" s="3">
+        <v>28200</v>
+      </c>
+      <c r="K54" s="3">
         <v>30600</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2451,8 +2578,11 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2468,8 +2598,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2485,35 +2616,36 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>800</v>
+      </c>
+      <c r="E57" s="3">
         <v>1200</v>
-      </c>
-      <c r="E57" s="3">
-        <v>7400</v>
       </c>
       <c r="F57" s="3">
         <v>1500</v>
       </c>
       <c r="G57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H57" s="3">
         <v>1400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2000</v>
       </c>
-      <c r="I57" s="3">
-        <v>1100</v>
-      </c>
       <c r="J57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K57" s="3">
         <v>2100</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2526,13 +2658,16 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
+      <c r="D58" s="3">
+        <v>0</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -2544,17 +2679,17 @@
         <v>0</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>5600</v>
       </c>
-      <c r="I58" s="3">
-        <v>5700</v>
-      </c>
       <c r="J58" s="3">
+        <v>7200</v>
+      </c>
+      <c r="K58" s="3">
         <v>4300</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2567,35 +2702,38 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F59" s="3">
+        <v>3300</v>
+      </c>
+      <c r="G59" s="3">
         <v>7100</v>
       </c>
-      <c r="E59" s="3">
-        <v>300</v>
-      </c>
-      <c r="F59" s="3">
-        <v>9400</v>
-      </c>
-      <c r="G59" s="3">
-        <v>9500</v>
-      </c>
       <c r="H59" s="3">
-        <v>12600</v>
+        <v>6800</v>
       </c>
       <c r="I59" s="3">
-        <v>10900</v>
+        <v>10200</v>
       </c>
       <c r="J59" s="3">
+        <v>10100</v>
+      </c>
+      <c r="K59" s="3">
         <v>11800</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2608,35 +2746,38 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E60" s="3">
         <v>8300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7700</v>
-      </c>
-      <c r="F60" s="3">
-        <v>10900</v>
       </c>
       <c r="G60" s="3">
         <v>10900</v>
       </c>
       <c r="H60" s="3">
+        <v>10900</v>
+      </c>
+      <c r="I60" s="3">
         <v>20200</v>
       </c>
-      <c r="I60" s="3">
-        <v>17700</v>
-      </c>
       <c r="J60" s="3">
+        <v>21100</v>
+      </c>
+      <c r="K60" s="3">
         <v>18100</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2649,8 +2790,11 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2690,8 +2834,11 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2699,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
         <v>100</v>
-      </c>
-      <c r="F62" s="3">
-        <v>300</v>
       </c>
       <c r="G62" s="3">
         <v>300</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
+      <c r="H62" s="3">
+        <v>300</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
@@ -2722,8 +2869,8 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -2731,8 +2878,11 @@
       <c r="O62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2772,8 +2922,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2813,8 +2966,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2854,35 +3010,38 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E66" s="3">
         <v>8300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>11200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>20200</v>
       </c>
-      <c r="I66" s="3">
-        <v>17700</v>
-      </c>
       <c r="J66" s="3">
+        <v>21100</v>
+      </c>
+      <c r="K66" s="3">
         <v>18100</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2895,8 +3054,11 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2912,8 +3074,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2953,8 +3116,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2994,8 +3160,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3035,8 +3204,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3076,35 +3248,38 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-32600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-31000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-29600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-28600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-26000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-12900</v>
       </c>
-      <c r="I72" s="3">
-        <v>-8700</v>
-      </c>
       <c r="J72" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="K72" s="3">
         <v>-6300</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3117,8 +3292,11 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3158,8 +3336,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3199,8 +3380,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3240,35 +3424,38 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E76" s="3">
         <v>15700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>17300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7000</v>
       </c>
-      <c r="I76" s="3">
-        <v>10800</v>
-      </c>
       <c r="J76" s="3">
+        <v>7100</v>
+      </c>
+      <c r="K76" s="3">
         <v>12400</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3281,8 +3468,11 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3322,95 +3512,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
-        <v>44926</v>
-      </c>
       <c r="J80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1400</v>
       </c>
-      <c r="E81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G81" s="3">
         <v>-2600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-10900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-200</v>
       </c>
-      <c r="I81" s="3">
-        <v>-4200</v>
-      </c>
       <c r="J81" s="3">
-        <v>-500</v>
+        <v>-4000</v>
       </c>
       <c r="K81" s="3">
         <v>-500</v>
       </c>
       <c r="L81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M81" s="3">
         <v>-700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2500</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3426,40 +3625,41 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>400</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0</v>
       </c>
       <c r="F83" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="G83" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="I83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3">
         <v>200</v>
-      </c>
-      <c r="K83" s="3">
-        <v>100</v>
       </c>
       <c r="L83" s="3">
         <v>100</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
+      <c r="M83" s="3">
+        <v>100</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
@@ -3467,8 +3667,11 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3508,8 +3711,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3549,8 +3755,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3590,8 +3799,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3631,8 +3843,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3672,49 +3887,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-500</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F89" s="3">
+        <v>400</v>
+      </c>
+      <c r="G89" s="3">
         <v>1200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>600</v>
       </c>
-      <c r="H89" s="3">
-        <v>4300</v>
-      </c>
       <c r="I89" s="3">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="J89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K89" s="3">
         <v>-3800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1000</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3730,19 +3951,20 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-900</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="F91" s="3">
-        <v>-600</v>
+        <v>-100</v>
       </c>
       <c r="G91" s="3">
         <v>-100</v>
@@ -3751,7 +3973,7 @@
         <v>-100</v>
       </c>
       <c r="I91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
@@ -3763,7 +3985,7 @@
         <v>-100</v>
       </c>
       <c r="M91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -3771,8 +3993,11 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3812,8 +4037,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3853,28 +4081,31 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
+      <c r="E94" s="3">
+        <v>-100</v>
       </c>
       <c r="F94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G94" s="3">
         <v>-300</v>
       </c>
-      <c r="G94" s="3">
-        <v>-700</v>
-      </c>
       <c r="H94" s="3">
-        <v>100</v>
+        <v>-600</v>
       </c>
       <c r="I94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J94" s="3">
         <v>-100</v>
@@ -3885,8 +4116,8 @@
       <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
+      <c r="M94" s="3">
+        <v>-100</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
@@ -3894,8 +4125,11 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3911,31 +4145,32 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3952,8 +4187,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3993,8 +4231,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4034,8 +4275,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4075,13 +4319,16 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>3</v>
@@ -4090,25 +4337,25 @@
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-3000</v>
       </c>
-      <c r="H100" s="3">
-        <v>-10400</v>
-      </c>
-      <c r="I100" s="3">
-        <v>400</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>7000</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
+      <c r="M100" s="3">
+        <v>0</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
@@ -4116,31 +4363,34 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4157,45 +4407,51 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-600</v>
       </c>
-      <c r="E102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-3100</v>
       </c>
-      <c r="H102" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-200</v>
-      </c>
       <c r="J102" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K102" s="3">
         <v>3000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1100</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PODC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PODC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
   <si>
     <t>PODC</t>
   </si>
@@ -656,213 +656,225 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E8" s="3">
         <v>12200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>13200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>11700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>10400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>10500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>10600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>16000</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E9" s="3">
         <v>11100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>11700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>9400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>9100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>13500</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>700</v>
+      </c>
+      <c r="E10" s="3">
         <v>1000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2500</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -879,8 +891,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -903,11 +916,11 @@
         <v>0</v>
       </c>
       <c r="J12" s="3">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3">
         <v>200</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
@@ -923,8 +936,11 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -967,20 +983,23 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>200</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
@@ -993,52 +1012,55 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>-2200</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>-600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-500</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>100</v>
+      </c>
+      <c r="E15" s="3">
         <v>300</v>
-      </c>
-      <c r="E15" s="3">
-        <v>400</v>
       </c>
       <c r="F15" s="3">
         <v>400</v>
       </c>
       <c r="G15" s="3">
+        <v>400</v>
+      </c>
+      <c r="H15" s="3">
         <v>300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>200</v>
       </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
       <c r="J15" s="3">
         <v>0</v>
       </c>
       <c r="K15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L15" s="3">
         <v>100</v>
@@ -1050,13 +1072,16 @@
         <v>100</v>
       </c>
       <c r="O15" s="3">
+        <v>100</v>
+      </c>
+      <c r="P15" s="3">
         <v>300</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,96 +1095,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E17" s="3">
         <v>13800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>14300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>12900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>13000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>11900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>10400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>9700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>18600</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1700</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-1200</v>
       </c>
       <c r="F18" s="3">
         <v>-1200</v>
       </c>
       <c r="G18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="H18" s="3">
         <v>-2600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2600</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1176,8 +1208,9 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1187,27 +1220,27 @@
       <c r="E20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3">
         <v>8800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>700</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1215,57 +1248,63 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-10000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-600</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3">
         <v>-2200</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1275,27 +1314,27 @@
       <c r="E22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3">
         <v>700</v>
-      </c>
-      <c r="I22" s="3">
-        <v>1600</v>
       </c>
       <c r="J22" s="3">
         <v>1600</v>
       </c>
       <c r="K22" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L22" s="3">
         <v>1400</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -1305,70 +1344,76 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-10900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4000</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-500</v>
       </c>
       <c r="L23" s="3">
         <v>-500</v>
       </c>
       <c r="M23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N23" s="3">
         <v>-700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2500</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F24" s="3">
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1378,8 +1423,8 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1396,8 +1441,11 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1440,96 +1488,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-10900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4000</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-500</v>
       </c>
       <c r="L26" s="3">
         <v>-500</v>
       </c>
       <c r="M26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N26" s="3">
         <v>-700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2500</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-10900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4000</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-500</v>
       </c>
       <c r="L27" s="3">
         <v>-500</v>
       </c>
       <c r="M27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N27" s="3">
         <v>-700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2500</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1572,8 +1629,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1616,8 +1676,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1660,8 +1723,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1704,8 +1770,11 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1715,27 +1784,27 @@
       <c r="E32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3">
         <v>-8800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-700</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -1743,57 +1812,63 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-10900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4000</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-500</v>
       </c>
       <c r="L33" s="3">
         <v>-500</v>
       </c>
       <c r="M33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N33" s="3">
         <v>-700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2500</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1836,101 +1911,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-10900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4000</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-500</v>
       </c>
       <c r="L35" s="3">
         <v>-500</v>
       </c>
       <c r="M35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N35" s="3">
         <v>-700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2500</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1947,8 +2031,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1965,38 +2050,39 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>600</v>
+      </c>
+      <c r="E41" s="3">
         <v>1400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>900</v>
-      </c>
-      <c r="F41" s="3">
-        <v>1400</v>
       </c>
       <c r="G41" s="3">
         <v>1400</v>
       </c>
       <c r="H41" s="3">
-        <v>500</v>
+        <v>1400</v>
       </c>
       <c r="I41" s="3">
         <v>500</v>
       </c>
       <c r="J41" s="3">
+        <v>500</v>
+      </c>
+      <c r="K41" s="3">
         <v>3600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4100</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2009,8 +2095,11 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2053,38 +2142,41 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E43" s="3">
         <v>6300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7100</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2097,8 +2189,11 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2123,8 +2218,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2141,8 +2236,11 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2167,12 +2265,12 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>700</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2185,38 +2283,41 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E46" s="3">
         <v>8300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12000</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2229,8 +2330,11 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2255,12 +2359,12 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3">
         <v>5500</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2273,8 +2377,11 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2291,7 +2398,7 @@
         <v>300</v>
       </c>
       <c r="H48" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I48" s="3">
         <v>200</v>
@@ -2302,8 +2409,8 @@
       <c r="K48" s="3">
         <v>200</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
+      <c r="L48" s="3">
+        <v>200</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
@@ -2317,37 +2424,40 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E49" s="3">
         <v>14200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>15200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>15100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>12700</v>
-      </c>
-      <c r="J49" s="3">
-        <v>12800</v>
       </c>
       <c r="K49" s="3">
         <v>12800</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
+      <c r="L49" s="3">
+        <v>12800</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
@@ -2361,8 +2471,11 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2405,8 +2518,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2449,34 +2565,37 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
         <v>300</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F52" s="3">
+      <c r="E52" s="3">
+        <v>300</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3">
         <v>100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2200</v>
-      </c>
-      <c r="I52" s="3">
-        <v>3800</v>
       </c>
       <c r="J52" s="3">
         <v>3800</v>
       </c>
       <c r="K52" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -2493,8 +2612,11 @@
       <c r="P52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2537,38 +2659,41 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E54" s="3">
         <v>23100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>24000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>24100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>27700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>28400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>27200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>28200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>30600</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2581,8 +2706,11 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2599,8 +2727,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2617,38 +2746,39 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E57" s="3">
         <v>800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1200</v>
-      </c>
-      <c r="F57" s="3">
-        <v>1500</v>
       </c>
       <c r="G57" s="3">
         <v>1500</v>
       </c>
       <c r="H57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I57" s="3">
         <v>1400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2100</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2661,8 +2791,11 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2682,17 +2815,17 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>5600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4300</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2705,38 +2838,41 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4400</v>
+        <v>3300</v>
       </c>
       <c r="E59" s="3">
         <v>4400</v>
       </c>
       <c r="F59" s="3">
+        <v>4400</v>
+      </c>
+      <c r="G59" s="3">
         <v>3300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>10200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11800</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2749,38 +2885,41 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E60" s="3">
         <v>7600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7700</v>
-      </c>
-      <c r="G60" s="3">
-        <v>10900</v>
       </c>
       <c r="H60" s="3">
         <v>10900</v>
       </c>
       <c r="I60" s="3">
+        <v>10900</v>
+      </c>
+      <c r="J60" s="3">
         <v>20200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>21100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>18100</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2793,8 +2932,11 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2837,28 +2979,31 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E62" s="3">
         <v>0</v>
       </c>
       <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
         <v>100</v>
-      </c>
-      <c r="G62" s="3">
-        <v>300</v>
       </c>
       <c r="H62" s="3">
         <v>300</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
+      <c r="I62" s="3">
+        <v>300</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
@@ -2872,8 +3017,8 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
+      <c r="N62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O62" s="3">
         <v>0</v>
@@ -2881,8 +3026,11 @@
       <c r="P62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2925,8 +3073,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2969,8 +3120,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3013,38 +3167,41 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E66" s="3">
         <v>7600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>11100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>20200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>21100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>18100</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3057,8 +3214,11 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3075,8 +3235,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3119,8 +3280,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3163,8 +3327,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3207,8 +3374,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3251,38 +3421,41 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-34200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-32600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-31000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-29600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-28600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-26000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-12900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-12700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-6300</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3295,8 +3468,11 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3339,8 +3515,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3383,8 +3562,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3427,38 +3609,41 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E76" s="3">
         <v>15500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>15700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>17300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12400</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3471,8 +3656,11 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3515,101 +3703,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-10900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4000</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-500</v>
       </c>
       <c r="L81" s="3">
         <v>-500</v>
       </c>
       <c r="M81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N81" s="3">
         <v>-700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2500</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3626,8 +3823,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3638,13 +3836,13 @@
         <v>0</v>
       </c>
       <c r="F83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G83" s="3">
         <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I83" s="3">
         <v>0</v>
@@ -3653,16 +3851,16 @@
         <v>0</v>
       </c>
       <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3">
         <v>200</v>
-      </c>
-      <c r="L83" s="3">
-        <v>100</v>
       </c>
       <c r="M83" s="3">
         <v>100</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
+      <c r="N83" s="3">
+        <v>100</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
@@ -3670,8 +3868,11 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3714,8 +3915,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3758,8 +3962,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3802,8 +4009,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3846,8 +4056,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3890,52 +4103,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E89" s="3">
         <v>500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>600</v>
       </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
       <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3">
         <v>-400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1000</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3952,13 +4171,14 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
@@ -3973,10 +4193,10 @@
         <v>-100</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
@@ -3988,7 +4208,7 @@
         <v>-100</v>
       </c>
       <c r="N91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
@@ -3996,8 +4216,11 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4040,8 +4263,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4084,31 +4310,34 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E94" s="3">
         <v>-100</v>
       </c>
       <c r="F94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G94" s="3">
         <v>-400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-600</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K94" s="3">
         <v>-100</v>
@@ -4119,8 +4348,8 @@
       <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
+      <c r="N94" s="3">
+        <v>-100</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
@@ -4128,8 +4357,11 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4146,8 +4378,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4172,8 +4405,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -4190,8 +4423,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4234,8 +4470,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4278,8 +4517,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4322,8 +4564,11 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4333,8 +4578,8 @@
       <c r="E100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G100" s="3">
         <v>0</v>
@@ -4343,22 +4588,22 @@
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-3000</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>7000</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
+      <c r="N100" s="3">
+        <v>0</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
@@ -4366,8 +4611,11 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4392,8 +4640,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4410,48 +4658,54 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E102" s="3">
         <v>500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-600</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>900</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-3100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1100</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PODC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PODC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="92">
   <si>
     <t>PODC</t>
   </si>
@@ -656,225 +656,251 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>14100</v>
+      </c>
+      <c r="F8" s="3">
         <v>12700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>12200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>13200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>11700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>10400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>10500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>10600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>8800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>8500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>8700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>8200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>8100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>16000</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>12600</v>
+      </c>
+      <c r="F9" s="3">
         <v>12000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>11100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>11700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>10700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>9400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>9100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>8200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>7600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>6300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>6600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>6700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>6000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>13500</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F10" s="3">
         <v>700</v>
-      </c>
-      <c r="E10" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1500</v>
       </c>
       <c r="G10" s="3">
         <v>1000</v>
       </c>
       <c r="H10" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J10" s="3">
         <v>1100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>1500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>2400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>1200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>2200</v>
-      </c>
-      <c r="M10" s="3">
-        <v>2100</v>
-      </c>
-      <c r="N10" s="3">
-        <v>1500</v>
       </c>
       <c r="O10" s="3">
         <v>2100</v>
       </c>
       <c r="P10" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>2100</v>
+      </c>
+      <c r="R10" s="3">
         <v>2500</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -892,8 +918,10 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -919,14 +947,14 @@
         <v>0</v>
       </c>
       <c r="K12" s="3">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3">
         <v>200</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
@@ -939,8 +967,14 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,25 +1020,31 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="E14" s="3">
         <v>200</v>
       </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+      <c r="H14" s="3">
+        <v>200</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
@@ -1015,26 +1055,32 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>-2200</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>-600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>-500</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1045,28 +1091,28 @@
         <v>300</v>
       </c>
       <c r="F15" s="3">
+        <v>100</v>
+      </c>
+      <c r="G15" s="3">
+        <v>300</v>
+      </c>
+      <c r="H15" s="3">
         <v>400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>200</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N15" s="3">
         <v>100</v>
@@ -1075,13 +1121,19 @@
         <v>100</v>
       </c>
       <c r="P15" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>100</v>
+      </c>
+      <c r="R15" s="3">
         <v>300</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,102 +1148,116 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>14300</v>
+        <v>16000</v>
       </c>
       <c r="E17" s="3">
-        <v>13800</v>
+        <v>15800</v>
       </c>
       <c r="F17" s="3">
         <v>14300</v>
       </c>
       <c r="G17" s="3">
+        <v>13800</v>
+      </c>
+      <c r="H17" s="3">
+        <v>14300</v>
+      </c>
+      <c r="I17" s="3">
         <v>12900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>13000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>11900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>10400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>9700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>8300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>9200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>8900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>8500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>18600</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-1600</v>
+        <v>-1100</v>
       </c>
       <c r="E18" s="3">
         <v>-1700</v>
       </c>
       <c r="F18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="H18" s="3">
         <v>-1200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-1200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-2600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-1400</v>
-      </c>
-      <c r="J18" s="3">
-        <v>200</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-800</v>
       </c>
       <c r="L18" s="3">
         <v>200</v>
       </c>
       <c r="M18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="N18" s="3">
+        <v>200</v>
+      </c>
+      <c r="O18" s="3">
         <v>-500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,8 +1275,10 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1223,88 +1291,100 @@
       <c r="F20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
         <v>8800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-1200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>1500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>700</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-1300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-2300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-10000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>1400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-2300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>1100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-600</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1317,120 +1397,132 @@
       <c r="F22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="3">
         <v>700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>1600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>1600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>1400</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-2600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-10900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-4000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
+      <c r="F24" s="3">
+        <v>0</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1444,8 +1536,14 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,102 +1589,120 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-2600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-10900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-4000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-2600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-10900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-4000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,8 +1748,14 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1679,8 +1801,14 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1854,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,8 +1907,14 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1787,88 +1927,100 @@
       <c r="F32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
         <v>-8800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>1200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-1500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-700</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-2600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-10900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-4000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,107 +2066,125 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-2600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-10900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-4000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2202,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,44 +2223,46 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F41" s="3">
         <v>600</v>
-      </c>
-      <c r="E41" s="3">
-        <v>1400</v>
-      </c>
-      <c r="F41" s="3">
-        <v>900</v>
       </c>
       <c r="G41" s="3">
         <v>1400</v>
       </c>
       <c r="H41" s="3">
+        <v>900</v>
+      </c>
+      <c r="I41" s="3">
         <v>1400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K41" s="3">
         <v>500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>3600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>4100</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2098,8 +2272,14 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2145,44 +2325,50 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F43" s="3">
         <v>5800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>6300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>7100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>6000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>7800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>9700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>8800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>6900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>7100</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2192,8 +2378,14 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2221,11 +2413,11 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2239,8 +2431,14 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2268,15 +2466,15 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>700</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2286,44 +2484,50 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>7600</v>
+      </c>
+      <c r="F46" s="3">
         <v>6600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>8300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>9200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>8600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>9600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>11200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>10400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>11400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>12000</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2333,8 +2537,14 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2362,15 +2572,15 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3">
         <v>5500</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2380,16 +2590,22 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E48" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F48" s="3">
         <v>300</v>
@@ -2401,10 +2617,10 @@
         <v>300</v>
       </c>
       <c r="I48" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J48" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K48" s="3">
         <v>200</v>
@@ -2412,11 +2628,11 @@
       <c r="L48" s="3">
         <v>200</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
+      <c r="M48" s="3">
+        <v>200</v>
+      </c>
+      <c r="N48" s="3">
+        <v>200</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
@@ -2427,44 +2643,50 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>13200</v>
+      </c>
+      <c r="F49" s="3">
         <v>13400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>14200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>14500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>15200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>15100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>14900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>12700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>12800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>12800</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2474,8 +2696,14 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2749,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,41 +2802,47 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>400</v>
+      </c>
+      <c r="F52" s="3">
         <v>300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>300</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3">
         <v>100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>2700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>2200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>3800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>3800</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
       <c r="N52" s="3">
         <v>0</v>
       </c>
@@ -2615,8 +2855,14 @@
       <c r="Q52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,44 +2908,50 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>21200</v>
+      </c>
+      <c r="F54" s="3">
         <v>20600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>23100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>24000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>24100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>27700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>28400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>27200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>28200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>30600</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2709,8 +2961,14 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +2986,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,44 +3007,46 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F57" s="3">
         <v>1000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>2100</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2794,8 +3056,14 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2818,20 +3086,20 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>5600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>7200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>4300</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2841,44 +3109,50 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F59" s="3">
         <v>3300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>4400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>4400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>3300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>7100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>6800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>10200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>10100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>11800</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2888,44 +3162,50 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6100</v>
+      </c>
+      <c r="F60" s="3">
         <v>5600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>7600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>8300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>7700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>10900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>10900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>20200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>21100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>18100</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2935,8 +3215,14 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2982,35 +3268,41 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
         <v>100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>300</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3020,17 +3312,23 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
-      <c r="P62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3374,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3427,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,44 +3480,50 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>6100</v>
+      </c>
+      <c r="F66" s="3">
         <v>5600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>7600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>8300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>7800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>11200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>11100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>20200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>21100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>18100</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3217,8 +3533,14 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3558,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3607,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3660,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3377,8 +3713,14 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,44 +3766,50 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-37100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-36100</v>
+      </c>
+      <c r="F72" s="3">
         <v>-34200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-32600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-31000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-29600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-28600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-26000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-12900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-12700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-6300</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3471,8 +3819,14 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +3872,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +3925,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,44 +3978,50 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>15100</v>
+      </c>
+      <c r="F76" s="3">
         <v>15000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>15500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>15700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>16300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>16500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>17300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>7000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>7100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>12400</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3659,8 +4031,14 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,107 +4084,125 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-2600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-10900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-4000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,55 +4220,63 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>100</v>
+      </c>
+      <c r="F83" s="3">
         <v>200</v>
       </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
       <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>100</v>
       </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
       <c r="K83" s="3">
         <v>0</v>
       </c>
       <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
         <v>200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>100</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4322,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4375,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4428,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4481,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,55 +4534,67 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-800</v>
+        <v>900</v>
       </c>
       <c r="E89" s="3">
         <v>500</v>
       </c>
       <c r="F89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="G89" s="3">
+        <v>500</v>
+      </c>
+      <c r="H89" s="3">
         <v>-500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>1200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>600</v>
       </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3">
         <v>-400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-3800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-1000</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,19 +4612,21 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
         <v>-100</v>
@@ -4196,13 +4638,13 @@
         <v>-100</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
       </c>
       <c r="L91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M91" s="3">
         <v>-100</v>
@@ -4211,16 +4653,22 @@
         <v>-100</v>
       </c>
       <c r="O91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4714,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,37 +4767,43 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-600</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-100</v>
-      </c>
       <c r="L94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M94" s="3">
         <v>-100</v>
@@ -4351,17 +4811,23 @@
       <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
+      <c r="O94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P94" s="3">
+        <v>-100</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,8 +4845,10 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4408,11 +4876,11 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -4426,8 +4894,14 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +4947,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +5000,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,8 +5053,14 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4581,41 +5073,47 @@
       <c r="F100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-3000</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>7000</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
+        <v>0</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4643,11 +5141,11 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -4661,51 +5159,63 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-800</v>
+        <v>800</v>
       </c>
       <c r="E102" s="3">
         <v>500</v>
       </c>
       <c r="F102" s="3">
+        <v>-800</v>
+      </c>
+      <c r="G102" s="3">
+        <v>500</v>
+      </c>
+      <c r="H102" s="3">
         <v>-600</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>900</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-3100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>3000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-1100</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PODC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PODC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="92">
   <si>
     <t>PODC</t>
   </si>
@@ -656,264 +656,276 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44834</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44742</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44651</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44561</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44469</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E8" s="3">
         <v>15200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>15000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>14100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>12700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>12200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>11700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>10400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>10500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>16000</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E9" s="3">
         <v>13500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>13600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>12000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>11100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>11700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>9100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>8200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>13500</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E10" s="3">
         <v>1600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2500</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -934,8 +946,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -970,11 +983,11 @@
         <v>0</v>
       </c>
       <c r="N12" s="3">
+        <v>0</v>
+      </c>
+      <c r="O12" s="3">
         <v>200</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
@@ -990,8 +1003,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1046,8 +1062,11 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1057,21 +1076,21 @@
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>200</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>200</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1084,64 +1103,67 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>-2200</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
         <v>-600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-500</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
         <v>100</v>
       </c>
       <c r="F15" s="3">
+        <v>100</v>
+      </c>
+      <c r="G15" s="3">
         <v>300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>300</v>
-      </c>
-      <c r="I15" s="3">
-        <v>400</v>
       </c>
       <c r="J15" s="3">
         <v>400</v>
       </c>
       <c r="K15" s="3">
+        <v>400</v>
+      </c>
+      <c r="L15" s="3">
         <v>300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>200</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
       <c r="O15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P15" s="3">
         <v>100</v>
@@ -1153,13 +1175,16 @@
         <v>100</v>
       </c>
       <c r="S15" s="3">
+        <v>100</v>
+      </c>
+      <c r="T15" s="3">
         <v>300</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1177,120 +1202,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E17" s="3">
         <v>16100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>16000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>15800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>14300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>14300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>12900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>13000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>18600</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1700</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-1200</v>
       </c>
       <c r="J18" s="3">
         <v>-1200</v>
       </c>
       <c r="K18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="L18" s="3">
         <v>-2600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2600</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1311,13 +1343,14 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>3</v>
@@ -1334,27 +1367,27 @@
       <c r="I20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3">
         <v>8800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>700</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -1362,69 +1395,75 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="E21" s="3">
         <v>-900</v>
       </c>
       <c r="F21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G21" s="3">
         <v>-1400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-10000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-600</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3">
         <v>-2200</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1446,27 +1485,27 @@
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3">
         <v>700</v>
-      </c>
-      <c r="M22" s="3">
-        <v>1600</v>
       </c>
       <c r="N22" s="3">
         <v>1600</v>
       </c>
       <c r="O22" s="3">
+        <v>1600</v>
+      </c>
+      <c r="P22" s="3">
         <v>1400</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
@@ -1476,67 +1515,73 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-10900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4000</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-500</v>
       </c>
       <c r="P23" s="3">
         <v>-500</v>
       </c>
       <c r="Q23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="R23" s="3">
         <v>-700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2500</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1546,8 +1591,8 @@
       <c r="E24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
@@ -1555,15 +1600,15 @@
       <c r="H24" s="3">
         <v>0</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1573,8 +1618,8 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -1591,8 +1636,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1647,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-10900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4000</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-500</v>
       </c>
       <c r="P26" s="3">
         <v>-500</v>
       </c>
       <c r="Q26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="R26" s="3">
         <v>-700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2500</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-10900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4000</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-500</v>
       </c>
       <c r="P27" s="3">
         <v>-500</v>
       </c>
       <c r="Q27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="R27" s="3">
         <v>-700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2500</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1815,8 +1872,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1871,8 +1931,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1927,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1983,13 +2049,16 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>3</v>
@@ -2006,27 +2075,27 @@
       <c r="I32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3">
         <v>-8800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-700</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -2034,69 +2103,75 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-10900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4000</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-500</v>
       </c>
       <c r="P33" s="3">
         <v>-500</v>
       </c>
       <c r="Q33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="R33" s="3">
         <v>-700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2500</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2151,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-10900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4000</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-500</v>
       </c>
       <c r="P35" s="3">
         <v>-500</v>
       </c>
       <c r="Q35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="R35" s="3">
         <v>-700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2500</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44834</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44742</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44651</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44561</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44469</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2290,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2312,50 +2397,51 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E41" s="3">
         <v>2700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>900</v>
-      </c>
-      <c r="J41" s="3">
-        <v>1400</v>
       </c>
       <c r="K41" s="3">
         <v>1400</v>
       </c>
       <c r="L41" s="3">
-        <v>500</v>
+        <v>1400</v>
       </c>
       <c r="M41" s="3">
         <v>500</v>
       </c>
       <c r="N41" s="3">
+        <v>500</v>
+      </c>
+      <c r="O41" s="3">
         <v>3600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4100</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2368,8 +2454,11 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2424,50 +2513,53 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7100</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2480,8 +2572,11 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2518,8 +2613,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -2536,8 +2631,11 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2574,12 +2672,12 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>700</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2592,50 +2690,53 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E46" s="3">
         <v>9200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>11400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12000</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2648,8 +2749,11 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2686,12 +2790,12 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3">
         <v>5500</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2704,13 +2808,16 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E48" s="3">
         <v>100</v>
@@ -2719,7 +2826,7 @@
         <v>100</v>
       </c>
       <c r="G48" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H48" s="3">
         <v>300</v>
@@ -2734,7 +2841,7 @@
         <v>300</v>
       </c>
       <c r="L48" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M48" s="3">
         <v>200</v>
@@ -2745,8 +2852,8 @@
       <c r="O48" s="3">
         <v>200</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
+      <c r="P48" s="3">
+        <v>200</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
@@ -2760,49 +2867,52 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E49" s="3">
         <v>13000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>13100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>13200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>13400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>15200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>15100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>12700</v>
-      </c>
-      <c r="N49" s="3">
-        <v>12800</v>
       </c>
       <c r="O49" s="3">
         <v>12800</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
+      <c r="P49" s="3">
+        <v>12800</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
@@ -2816,8 +2926,11 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2872,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,13 +3044,16 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>400</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E52" s="3">
         <v>400</v>
@@ -2943,31 +3062,31 @@
         <v>400</v>
       </c>
       <c r="G52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H52" s="3">
         <v>300</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="I52" s="3">
+        <v>300</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K52" s="3">
         <v>100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2200</v>
-      </c>
-      <c r="M52" s="3">
-        <v>3800</v>
       </c>
       <c r="N52" s="3">
         <v>3800</v>
       </c>
       <c r="O52" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
@@ -2984,8 +3103,11 @@
       <c r="T52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3040,50 +3162,53 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E54" s="3">
         <v>22600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>22300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>21200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>20600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>23100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>24000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>24100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>27700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>28400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>27200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>28200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>30600</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3096,8 +3221,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3118,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3140,50 +3269,51 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E57" s="3">
         <v>1500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1200</v>
-      </c>
-      <c r="J57" s="3">
-        <v>1500</v>
       </c>
       <c r="K57" s="3">
         <v>1500</v>
       </c>
       <c r="L57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M57" s="3">
         <v>1400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2100</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3196,13 +3326,16 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -3229,17 +3362,17 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>5600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4300</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3252,50 +3385,53 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E59" s="3">
         <v>5500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3300</v>
-      </c>
-      <c r="H59" s="3">
-        <v>4400</v>
       </c>
       <c r="I59" s="3">
         <v>4400</v>
       </c>
       <c r="J59" s="3">
+        <v>4400</v>
+      </c>
+      <c r="K59" s="3">
         <v>3300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11800</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3308,50 +3444,53 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E60" s="3">
         <v>7900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7700</v>
-      </c>
-      <c r="K60" s="3">
-        <v>10900</v>
       </c>
       <c r="L60" s="3">
         <v>10900</v>
       </c>
       <c r="M60" s="3">
+        <v>10900</v>
+      </c>
+      <c r="N60" s="3">
         <v>20200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>21100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>18100</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3364,13 +3503,16 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
@@ -3420,8 +3562,11 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3437,23 +3582,23 @@
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H62" s="3">
-        <v>0</v>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I62" s="3">
         <v>0</v>
       </c>
       <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3">
         <v>100</v>
-      </c>
-      <c r="K62" s="3">
-        <v>300</v>
       </c>
       <c r="L62" s="3">
         <v>300</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
+      <c r="M62" s="3">
+        <v>300</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
@@ -3467,8 +3612,8 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R62" s="3">
-        <v>0</v>
+      <c r="R62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S62" s="3">
         <v>0</v>
@@ -3476,8 +3621,11 @@
       <c r="T62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3532,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3588,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3644,50 +3798,53 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E66" s="3">
         <v>7900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>8300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>20200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>21100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>18100</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3700,8 +3857,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3722,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3778,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3834,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3890,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3946,50 +4116,53 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-38300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-38100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-37100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-36100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-34200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-32600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-31000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-29600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-28600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-26000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-12900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-12700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-6300</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4002,8 +4175,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4058,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4114,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4170,50 +4352,53 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>14700</v>
+        <v>15800</v>
       </c>
       <c r="E76" s="3">
         <v>14700</v>
       </c>
       <c r="F76" s="3">
+        <v>14700</v>
+      </c>
+      <c r="G76" s="3">
         <v>15100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>15000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>15500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>15700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>17300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>12400</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4226,8 +4411,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4282,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44834</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44742</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44651</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44561</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44469</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-10900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4000</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-500</v>
       </c>
       <c r="P81" s="3">
         <v>-500</v>
       </c>
       <c r="Q81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="R81" s="3">
         <v>-700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2500</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4421,37 +4618,38 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>100</v>
+      </c>
+      <c r="E83" s="3">
         <v>400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>200</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
       <c r="I83" s="3">
         <v>0</v>
       </c>
       <c r="J83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K83" s="3">
         <v>100</v>
       </c>
       <c r="L83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -4460,16 +4658,16 @@
         <v>0</v>
       </c>
       <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
         <v>200</v>
-      </c>
-      <c r="P83" s="3">
-        <v>100</v>
       </c>
       <c r="Q83" s="3">
         <v>100</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
+      <c r="R83" s="3">
+        <v>100</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
@@ -4477,8 +4675,11 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4533,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4589,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4645,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4701,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4757,64 +4970,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="E89" s="3">
         <v>900</v>
       </c>
       <c r="F89" s="3">
+        <v>900</v>
+      </c>
+      <c r="G89" s="3">
         <v>500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>600</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
       <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3">
         <v>-400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1000</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4835,25 +5054,26 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3">
         <v>-100</v>
@@ -4868,10 +5088,10 @@
         <v>-100</v>
       </c>
       <c r="M91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O91" s="3">
         <v>-100</v>
@@ -4883,7 +5103,7 @@
         <v>-100</v>
       </c>
       <c r="R91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -4891,8 +5111,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4947,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5003,43 +5229,46 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
       <c r="H94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I94" s="3">
         <v>-100</v>
       </c>
       <c r="J94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-600</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O94" s="3">
         <v>-100</v>
@@ -5050,8 +5279,8 @@
       <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
+      <c r="R94" s="3">
+        <v>-100</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
@@ -5059,8 +5288,11 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5081,8 +5313,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5119,8 +5352,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -5137,8 +5370,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5193,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5249,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5305,8 +5547,11 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5328,8 +5573,8 @@
       <c r="I100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -5338,22 +5583,22 @@
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-3000</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>7000</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
+      <c r="R100" s="3">
+        <v>0</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
@@ -5361,8 +5606,11 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5399,8 +5647,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -5417,60 +5665,66 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>700</v>
+      </c>
+      <c r="E102" s="3">
         <v>900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-600</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>900</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>-3100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1100</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
